--- a/diseases/d241/2026-2029.xlsx
+++ b/diseases/d241/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>268</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>4.740855213131956</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>245</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>4.33399077319899</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>343</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>6.067587082478586</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>226</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>3.997885366297844</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>137</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>2.423496881339843</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>217</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>3.838677541976248</v>
       </c>
@@ -3136,16 +3118,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O14" t="n">
-        <v>278</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="R14" t="n">
-        <v>4.917752795711507</v>
+        <v>4.935442553969462</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -3298,10 +3277,10 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O15" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3532,16 +3511,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="O16" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4245541981909216</v>
+        <v>1.928183650117102</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3694,10 +3670,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="O17" t="n">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -4039,7 +4015,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1738</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d241/2026-2029.xlsx
+++ b/diseases/d241/2026-2029.xlsx
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="O16" t="n">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="R16" t="n">
-        <v>1.928183650117102</v>
+        <v>3.520261893333057</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="O17" t="n">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1824</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d241/2026-2029.xlsx
+++ b/diseases/d241/2026-2029.xlsx
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>199</v>
+        <v>304</v>
       </c>
       <c r="O16" t="n">
-        <v>199</v>
+        <v>304</v>
       </c>
       <c r="R16" t="n">
-        <v>3.520261893333057</v>
+        <v>5.377686510418338</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>199</v>
+        <v>304</v>
       </c>
       <c r="O17" t="n">
-        <v>199</v>
+        <v>304</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1914</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d241/2026-2029.xlsx
+++ b/diseases/d241/2026-2029.xlsx
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>304</v>
+        <v>380</v>
       </c>
       <c r="O16" t="n">
-        <v>304</v>
+        <v>380</v>
       </c>
       <c r="R16" t="n">
-        <v>5.377686510418338</v>
+        <v>6.722108138022924</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>304</v>
+        <v>380</v>
       </c>
       <c r="O17" t="n">
-        <v>304</v>
+        <v>380</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3832,6 +3832,399 @@
         </is>
       </c>
       <c r="BC17" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D241</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>escherichia-coli-enteritis,-all-reported-pathotypes</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Escherichia coli enteritis, all reported pathotypes</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D241</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Escherichia coli enteritis, all reported pathotypes</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>大肠埃希菌肠炎（所有报告型别）</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.08844879128977531</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_304_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_304_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D241</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>escherichia-coli-enteritis,-all-reported-pathotypes</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Escherichia coli enteritis, all reported pathotypes</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D241</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Escherichia coli enteritis, all reported pathotypes</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>大肠埃希菌肠炎（所有报告型别）</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_304_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_304_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>E. coli-enteritt</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS aggregate includes EHEC/STEC and other reportable pathotypes; do not add to D115.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_304_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -3870,7 +4263,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -3953,7 +4346,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -3963,7 +4356,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -3983,7 +4376,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -4015,7 +4408,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2019</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="16">
